--- a/TestData/Orders.xlsx
+++ b/TestData/Orders.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>Order ID</t>
   </si>
@@ -36,6 +36,63 @@
   </si>
   <si>
     <t>2026-03-26 13:27:32</t>
+  </si>
+  <si>
+    <t>2004341815</t>
+  </si>
+  <si>
+    <t>2026-03-26 15:39:17</t>
+  </si>
+  <si>
+    <t>2004341816</t>
+  </si>
+  <si>
+    <t>2026-03-26 15:45:37</t>
+  </si>
+  <si>
+    <t>2004341817</t>
+  </si>
+  <si>
+    <t>2026-03-26 16:13:37</t>
+  </si>
+  <si>
+    <t>2004341818</t>
+  </si>
+  <si>
+    <t>2026-03-26 16:15:58</t>
+  </si>
+  <si>
+    <t>8091146</t>
+  </si>
+  <si>
+    <t>Subscription</t>
+  </si>
+  <si>
+    <t>2026-03-26 16:25:46</t>
+  </si>
+  <si>
+    <t>8091147</t>
+  </si>
+  <si>
+    <t>2026-03-26 16:44:44</t>
+  </si>
+  <si>
+    <t>2004341820</t>
+  </si>
+  <si>
+    <t>2026-03-26 16:59:03</t>
+  </si>
+  <si>
+    <t>8091148</t>
+  </si>
+  <si>
+    <t>2026-03-26 17:00:22</t>
+  </si>
+  <si>
+    <t>2004341822</t>
+  </si>
+  <si>
+    <t>2026-03-26 17:15:22</t>
   </si>
 </sst>
 </file>
@@ -80,7 +137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -116,6 +173,105 @@
         <v>7</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/TestData/Orders.xlsx
+++ b/TestData/Orders.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>Order ID</t>
   </si>
@@ -93,6 +93,24 @@
   </si>
   <si>
     <t>2026-03-26 17:15:22</t>
+  </si>
+  <si>
+    <t>8091149</t>
+  </si>
+  <si>
+    <t>2026-03-26 17:34:40</t>
+  </si>
+  <si>
+    <t>2004341823</t>
+  </si>
+  <si>
+    <t>2026-03-26 17:56:20</t>
+  </si>
+  <si>
+    <t>8091150</t>
+  </si>
+  <si>
+    <t>2026-03-26 17:57:37</t>
   </si>
 </sst>
 </file>
@@ -137,7 +155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -272,6 +290,39 @@
         <v>26</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
